--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F87709C8-4C01-4C32-B5D0-EB299419B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7715611F-5F61-4A57-B0F1-907502D6BF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,13 +687,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH03,S03aH02,S01aH02,S04aH04,S02aH03,S02aH02,S03aH03,S01aH04,S02aH04,S02aH05,S03aH05,S04aH03,S01aH05,S04aH02,S03aH04,S04aH05</t>
+    <t>S01aH04,S02aH04,S02aH05,S04aH03,S01aH03,S03aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH05,S04aH02,S02aH03,S04aH05,S03aH05,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S02aH01,S01aH06</t>
+    <t>S02aH06,S02aH01,S03aH06,S01aH06,S01aH01,S04aH01,S04aH06,S03aH01</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S02aH06,S02aH01,S01aH06</v>
+        <v>S02aH06,S02aH01,S03aH06,S01aH06,S01aH01,S04aH01,S04aH06,S03aH01</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S01aH03,S03aH02,S01aH02,S04aH04,S02aH03,S02aH02,S03aH03,S01aH04,S02aH04,S02aH05,S03aH05,S04aH03,S01aH05,S04aH02,S03aH04,S04aH05</v>
+        <v>S01aH04,S02aH04,S02aH05,S04aH03,S01aH03,S03aH02,S01aH02,S04aH04,S03aH04,S03aH03,S01aH05,S04aH02,S02aH03,S04aH05,S03aH05,S02aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1416,7 +1416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{736A4FCD-3792-41A2-80D6-799DEA2B1C02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B00C9DC1-4DEE-4903-ABDE-271BFE58C746}">
   <dimension ref="A9:G16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1522,7 +1522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDC8BC3F-3392-4ABA-B589-8858CE1665DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBBEEFB-2BBB-48D1-95E8-3CD514B1A51F}">
   <dimension ref="B9:O682"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -20496,7 +20496,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3834ED25-1BEF-4C55-A08E-A0CA136F3571}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED37AC54-4F51-4889-899F-E50892D5E94C}">
   <dimension ref="B9:DH71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31506,7 +31506,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C92BCBA1-9CE5-4C47-9257-7E10436CBE0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA0E91A3-DB8E-4054-98F6-DCA0B5287DAD}">
   <dimension ref="B9:E34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -31872,7 +31872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53019DB6-3563-4C57-97CA-B3BC6842E8D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5522AA38-117E-4D24-8159-696E5ADC7274}">
   <dimension ref="B9:D58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32427,7 +32427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F606CBB6-11E8-4E8B-A1CA-B45BC6B2AAD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189F3EEB-195D-49C5-AE6F-DE926F888E56}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32718,7 +32718,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F68F4673-3298-4968-926D-3E53E7A5508C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2FCF50-0F91-4648-A3F4-C2E676B66EA4}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -32890,7 +32890,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.40566666666666668</v>
+        <v>0.40566666666666662</v>
       </c>
       <c r="E21" t="s">
         <v>223</v>
@@ -32960,7 +32960,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.41706666666666664</v>
+        <v>0.4170666666666667</v>
       </c>
       <c r="E26" t="s">
         <v>223</v>
@@ -33002,7 +33002,7 @@
         <v>43</v>
       </c>
       <c r="D29">
-        <v>0.47366666666666668</v>
+        <v>0.47366666666666662</v>
       </c>
       <c r="E29" t="s">
         <v>223</v>
@@ -33128,7 +33128,7 @@
         <v>45</v>
       </c>
       <c r="D38">
-        <v>0.4916666666666667</v>
+        <v>0.49166666666666664</v>
       </c>
       <c r="E38" t="s">
         <v>223</v>
@@ -33170,7 +33170,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.42980000000000002</v>
+        <v>0.42979999999999996</v>
       </c>
       <c r="E41" t="s">
         <v>223</v>
@@ -33408,7 +33408,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.35393333333333338</v>
+        <v>0.35393333333333327</v>
       </c>
       <c r="E58" t="s">
         <v>223</v>
@@ -33506,7 +33506,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.40646666666666659</v>
+        <v>0.4064666666666667</v>
       </c>
       <c r="E65" t="s">
         <v>223</v>
@@ -33520,7 +33520,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.34656666666666663</v>
+        <v>0.34656666666666669</v>
       </c>
       <c r="E66" t="s">
         <v>223</v>
@@ -33576,7 +33576,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.40836666666666671</v>
+        <v>0.4083666666666666</v>
       </c>
       <c r="E70" t="s">
         <v>223</v>
@@ -33730,7 +33730,7 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>0.53039999999999998</v>
+        <v>0.53039999999999987</v>
       </c>
       <c r="E81" t="s">
         <v>223</v>
@@ -33786,7 +33786,7 @@
         <v>43</v>
       </c>
       <c r="D85">
-        <v>0.41486666666666672</v>
+        <v>0.41486666666666666</v>
       </c>
       <c r="E85" t="s">
         <v>223</v>
@@ -33800,7 +33800,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.38400000000000006</v>
+        <v>0.38399999999999995</v>
       </c>
       <c r="E86" t="s">
         <v>223</v>
@@ -33898,7 +33898,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.49019999999999997</v>
+        <v>0.49020000000000002</v>
       </c>
       <c r="E93" t="s">
         <v>223</v>
@@ -33954,7 +33954,7 @@
         <v>43</v>
       </c>
       <c r="D97">
-        <v>0.47839999999999994</v>
+        <v>0.47839999999999999</v>
       </c>
       <c r="E97" t="s">
         <v>223</v>
@@ -33968,7 +33968,7 @@
         <v>45</v>
       </c>
       <c r="D98">
-        <v>0.42363333333333336</v>
+        <v>0.42363333333333331</v>
       </c>
       <c r="E98" t="s">
         <v>223</v>
@@ -34010,7 +34010,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.53829999999999989</v>
+        <v>0.5383</v>
       </c>
       <c r="E101" t="s">
         <v>223</v>
@@ -34122,7 +34122,7 @@
         <v>43</v>
       </c>
       <c r="D109">
-        <v>0.43163333333333331</v>
+        <v>0.43163333333333337</v>
       </c>
       <c r="E109" t="s">
         <v>223</v>
@@ -34136,7 +34136,7 @@
         <v>45</v>
       </c>
       <c r="D110">
-        <v>0.49236666666666667</v>
+        <v>0.49236666666666662</v>
       </c>
       <c r="E110" t="s">
         <v>223</v>
@@ -34192,7 +34192,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.45659999999999995</v>
+        <v>0.45660000000000006</v>
       </c>
       <c r="E114" t="s">
         <v>223</v>
@@ -34248,7 +34248,7 @@
         <v>45</v>
       </c>
       <c r="D118">
-        <v>0.38423333333333326</v>
+        <v>0.38423333333333337</v>
       </c>
       <c r="E118" t="s">
         <v>223</v>
